--- a/registry/export_registry.xlsx
+++ b/registry/export_registry.xlsx
@@ -987,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,30 +1023,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>domains</t>
+          <t>description</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name_cn</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>name_cn</t>
+          <t>name_en</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>name_en</t>
+          <t>source</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -1081,7 +1076,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1089,18 +1084,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1135,7 +1125,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>供应商编码</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1143,18 +1133,13 @@
           <t>供应商编码</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>供应商编码</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1189,7 +1174,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>供应商名称</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1197,18 +1182,13 @@
           <t>供应商名称</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>供应商名称</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1243,7 +1223,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>供应商状态</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1251,18 +1231,13 @@
           <t>供应商状态</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>供应商状态</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1297,7 +1272,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>创建时间</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1305,18 +1280,13 @@
           <t>创建时间</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1351,7 +1321,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1359,18 +1329,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1409,7 +1374,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>供应商ID</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,18 +1382,13 @@
           <t>供应商ID</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1463,7 +1423,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>资质类型</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1471,18 +1431,13 @@
           <t>资质类型</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>资质类型</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1517,7 +1472,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["supply_base"]</t>
+          <t>有效期至</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1525,18 +1480,13 @@
           <t>有效期至</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>有效期至</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1571,7 +1521,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1579,18 +1529,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1625,7 +1570,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>采购订单编号</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1633,18 +1578,13 @@
           <t>采购订单编号</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>采购订单编号</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1683,7 +1623,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["po_management", "supply_base"]</t>
+          <t>供应商ID</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1691,18 +1631,13 @@
           <t>供应商ID</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1741,7 +1676,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>合同ID</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1749,18 +1684,13 @@
           <t>合同ID</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>合同ID</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1795,7 +1725,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>订单总金额</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1803,18 +1733,13 @@
           <t>订单总金额</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>订单总金额</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1849,7 +1774,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>币种</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1857,18 +1782,13 @@
           <t>币种</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>币种</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1903,7 +1823,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>订单状态</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1911,18 +1831,13 @@
           <t>订单状态</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>订单状态</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1957,7 +1872,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>创建时间</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1965,18 +1880,13 @@
           <t>创建时间</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2011,7 +1921,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2019,18 +1929,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2069,7 +1974,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>所属采购订单ID</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2077,18 +1982,13 @@
           <t>所属采购订单ID</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>所属采购订单ID</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2123,7 +2023,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>行号</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2131,18 +2031,13 @@
           <t>行号</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>行号</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2177,7 +2072,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>物料编码</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2185,18 +2080,13 @@
           <t>物料编码</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2231,7 +2121,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>采购数量</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2239,18 +2129,13 @@
           <t>采购数量</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>采购数量</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2285,7 +2170,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>单价</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2293,18 +2178,13 @@
           <t>单价</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2339,7 +2219,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>行金额</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2347,18 +2227,13 @@
           <t>行金额</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>行金额</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2393,7 +2268,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2401,18 +2276,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2447,7 +2317,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>合同编号</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2455,18 +2325,13 @@
           <t>合同编号</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>合同编号</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2505,7 +2370,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["po_management", "supply_base"]</t>
+          <t>供应商ID</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2513,18 +2378,13 @@
           <t>供应商ID</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>供应商ID</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2559,7 +2419,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>合同金额</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2567,18 +2427,13 @@
           <t>合同金额</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>合同金额</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2613,7 +2468,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>生效日期</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2621,18 +2476,13 @@
           <t>生效日期</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>生效日期</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2667,7 +2517,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>到期日期</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2675,18 +2525,13 @@
           <t>到期日期</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>到期日期</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2721,7 +2566,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2729,18 +2574,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2779,7 +2619,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>采购订单行ID</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2787,18 +2627,13 @@
           <t>采购订单行ID</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>采购订单行ID</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2833,7 +2668,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>实收数量</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2841,18 +2676,13 @@
           <t>实收数量</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>实收数量</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2887,7 +2717,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>["po_management"]</t>
+          <t>收货日期</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2895,18 +2725,13 @@
           <t>收货日期</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>收货日期</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2941,7 +2766,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2949,18 +2774,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -2995,7 +2815,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>发票号码</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3003,18 +2823,13 @@
           <t>发票号码</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>发票号码</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3053,7 +2868,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>["finance", "po_management"]</t>
+          <t>采购订单ID</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3061,18 +2876,13 @@
           <t>采购订单ID</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>采购订单ID</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3107,7 +2917,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>发票金额</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3115,18 +2925,13 @@
           <t>发票金额</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>发票金额</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3161,7 +2966,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>税额</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3169,18 +2974,13 @@
           <t>税额</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>税额</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3215,7 +3015,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>开票日期</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3223,18 +3023,13 @@
           <t>开票日期</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>开票日期</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3269,7 +3064,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3277,18 +3072,13 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3327,7 +3117,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>发票ID</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3335,18 +3125,13 @@
           <t>发票ID</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>发票ID</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3381,7 +3166,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>付款金额</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3389,18 +3174,13 @@
           <t>付款金额</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>付款金额</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3435,7 +3215,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>["finance"]</t>
+          <t>付款日期</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3443,18 +3223,13 @@
           <t>付款日期</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>付款日期</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3471,7 +3246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3721,7 +3496,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3753,7 +3528,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3785,7 +3560,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3817,7 +3592,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3849,7 +3624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3881,7 +3656,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3913,7 +3688,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3945,7 +3720,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3957,17 +3732,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>proc.public.supplier</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>proc.public.supplier.id</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3977,7 +3752,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3989,17 +3764,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>proc.public.supplier</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>proc.public.supplier.code</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4009,7 +3784,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4021,17 +3796,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>proc.public.supplier</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>proc.public.supplier.name</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4041,7 +3816,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4053,17 +3828,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>proc.public.supplier</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>proc.public.supplier.status</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4073,7 +3848,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4085,17 +3860,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>proc.public.supplier</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>proc.public.supplier.created_at</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4105,7 +3880,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4117,17 +3892,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>proc.public.supplier_qual</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>proc.public.supplier_qual.id</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4137,7 +3912,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4149,17 +3924,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>proc.public.supplier_qual</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>proc.public.supplier_qual.supplier_id</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4169,7 +3944,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4181,17 +3956,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>proc.public.supplier_qual</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>proc.public.supplier_qual.qual_type</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4201,7 +3976,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4213,17 +3988,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>proc.public.supplier_qual</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>proc.public.supplier_qual.expire_date</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>supply_base</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4233,7 +4008,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4245,17 +4020,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>proc.public.po_order.id</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>po_management</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4265,7 +4040,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4277,17 +4052,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>proc.public.po_order.order_no</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>po_management</t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4297,7 +4072,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4309,17 +4084,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>proc.public.po_order</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>proc.public.po_order.supplier_id</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>po_management</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4329,7 +4104,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4341,17 +4116,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>proc.public.po_order.supplier_id</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>supply_base</t>
+          <t>proc.public.po_order.contract_id</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4361,7 +4136,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4373,17 +4148,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>proc.public.po_order.contract_id</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_order.total_amt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4393,7 +4168,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4405,17 +4180,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>proc.public.po_order.total_amt</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_order.currency</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4425,7 +4200,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4437,17 +4212,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>proc.public.po_order.currency</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_order.status</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4457,7 +4232,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4469,17 +4244,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>proc.public.po_order.status</t>
+          <t>proc.public.po_order</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_order.created_at</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4489,7 +4264,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4501,17 +4276,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>proc.public.po_order.created_at</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_line.id</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4521,7 +4296,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4533,17 +4308,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>proc.public.po_line.id</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_line.po_order_id</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4553,7 +4328,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4565,17 +4340,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>proc.public.po_line.po_order_id</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_line.line_no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4585,7 +4360,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4597,17 +4372,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>proc.public.po_line.line_no</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_line.material_code</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4617,7 +4392,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4629,17 +4404,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>proc.public.po_line.material_code</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_line.quantity</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4649,7 +4424,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4661,17 +4436,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>proc.public.po_line.quantity</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_line.unit_price</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4681,7 +4456,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4693,17 +4468,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>proc.public.po_line.unit_price</t>
+          <t>proc.public.po_line</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.po_line.line_amt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4713,7 +4488,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4725,17 +4500,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>proc.public.po_line.line_amt</t>
+          <t>proc.public.contract</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.contract.id</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4745,7 +4520,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4757,17 +4532,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>proc.public.contract.id</t>
+          <t>proc.public.contract</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.contract.contract_no</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4777,7 +4552,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4789,17 +4564,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>proc.public.contract.contract_no</t>
+          <t>proc.public.contract</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.contract.supplier_id</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4809,7 +4584,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4821,17 +4596,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>proc.public.contract.supplier_id</t>
+          <t>proc.public.contract</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.contract.total_amt</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4841,7 +4616,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4853,17 +4628,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>proc.public.contract.supplier_id</t>
+          <t>proc.public.contract</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>supply_base</t>
+          <t>proc.public.contract.start_date</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4873,7 +4648,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4885,17 +4660,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>proc.public.contract.total_amt</t>
+          <t>proc.public.contract</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.contract.end_date</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4905,7 +4680,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4917,17 +4692,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>proc.public.contract.start_date</t>
+          <t>proc.public.goods_receipt</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.goods_receipt.id</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4937,7 +4712,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4949,17 +4724,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>proc.public.contract.end_date</t>
+          <t>proc.public.goods_receipt</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.goods_receipt.po_line_id</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4969,7 +4744,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4981,17 +4756,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.id</t>
+          <t>proc.public.goods_receipt</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.goods_receipt.receipt_qty</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5001,7 +4776,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5013,17 +4788,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.po_line_id</t>
+          <t>proc.public.goods_receipt</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.goods_receipt.receipt_date</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5033,7 +4808,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5045,17 +4820,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.receipt_qty</t>
+          <t>proc.public.invoice</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.invoice.id</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5065,7 +4840,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5077,17 +4852,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>proc.public.goods_receipt.receipt_date</t>
+          <t>proc.public.invoice</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.invoice.invoice_no</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5097,7 +4872,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5109,17 +4884,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>proc.public.invoice.id</t>
+          <t>proc.public.invoice</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.invoice.po_order_id</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5129,7 +4904,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5141,17 +4916,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>proc.public.invoice.invoice_no</t>
+          <t>proc.public.invoice</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.invoice.amount</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5161,7 +4936,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5173,17 +4948,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>proc.public.invoice.po_order_id</t>
+          <t>proc.public.invoice</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.invoice.tax_amt</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5193,7 +4968,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5205,17 +4980,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>proc.public.invoice.po_order_id</t>
+          <t>proc.public.invoice</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>po_management</t>
+          <t>proc.public.invoice.invoice_date</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5225,7 +5000,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5237,17 +5012,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>proc.public.invoice.amount</t>
+          <t>proc.public.payment</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.payment.id</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5257,7 +5032,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5269,17 +5044,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>proc.public.invoice.tax_amt</t>
+          <t>proc.public.payment</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.payment.invoice_id</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5289,7 +5064,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5301,17 +5076,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>proc.public.invoice.invoice_date</t>
+          <t>proc.public.payment</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.payment.pay_amt</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5321,7 +5096,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5333,17 +5108,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>proc.public.payment.id</t>
+          <t>proc.public.payment</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.payment.pay_date</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>HAS_COLUMN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5353,7 +5128,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5365,17 +5140,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>proc.public.payment.invoice_id</t>
+          <t>proc.public.supplier_qual.supplier_id</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.supplier.id</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5385,7 +5160,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5397,17 +5172,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>proc.public.payment.pay_amt</t>
+          <t>proc.public.po_order.supplier_id</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.supplier.id</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5417,7 +5192,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5429,17 +5204,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>proc.public.payment.pay_date</t>
+          <t>proc.public.po_order.contract_id</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>proc.public.contract.id</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IN_DOMAIN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5449,7 +5224,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5461,17 +5236,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>proc.public.po_line.po_order_id</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>proc.public.supplier.id</t>
+          <t>proc.public.po_order.id</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HAS_COLUMN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5481,7 +5256,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5493,17 +5268,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>proc.public.contract.supplier_id</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>proc.public.supplier.code</t>
+          <t>proc.public.supplier.id</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HAS_COLUMN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5513,7 +5288,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5525,17 +5300,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>proc.public.goods_receipt.po_line_id</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>proc.public.supplier.name</t>
+          <t>proc.public.po_line.id</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HAS_COLUMN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5545,7 +5320,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5557,17 +5332,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>proc.public.invoice.po_order_id</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>proc.public.supplier.status</t>
+          <t>proc.public.po_order.id</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HAS_COLUMN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5577,7 +5352,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5589,17 +5364,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>proc.public.supplier</t>
+          <t>proc.public.payment.invoice_id</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>proc.public.supplier.created_at</t>
+          <t>proc.public.invoice.id</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HAS_COLUMN</t>
+          <t>REFERENCES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5609,1514 +5384,10 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.id</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.supplier_id</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.qual_type</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.expire_date</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.id</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.order_no</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.supplier_id</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.contract_id</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.total_amt</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.currency</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.status</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>proc.public.po_order</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.created_at</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>proc.public.po_line</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.id</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>proc.public.po_line</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.po_order_id</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>proc.public.po_line</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.line_no</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>proc.public.po_line</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.material_code</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>proc.public.po_line</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.quantity</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>proc.public.po_line</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.unit_price</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>proc.public.po_line</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.line_amt</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>proc.public.contract</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>proc.public.contract.id</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>proc.public.contract</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>proc.public.contract.contract_no</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>proc.public.contract</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>proc.public.contract.supplier_id</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>proc.public.contract</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>proc.public.contract.total_amt</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>proc.public.contract</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>proc.public.contract.start_date</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>proc.public.contract</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>proc.public.contract.end_date</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt.id</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt.po_line_id</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt.receipt_qty</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt.receipt_date</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>proc.public.invoice</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.id</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>proc.public.invoice</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.invoice_no</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>proc.public.invoice</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.po_order_id</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>proc.public.invoice</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.amount</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>proc.public.invoice</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.tax_amt</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>proc.public.invoice</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.invoice_date</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>proc.public.payment</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>proc.public.payment.id</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>proc.public.payment</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>proc.public.payment.invoice_id</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>proc.public.payment</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>proc.public.payment.pay_amt</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>proc.public.payment</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>proc.public.payment.pay_date</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>HAS_COLUMN</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>proc.public.supplier_qual.supplier_id</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.id</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.supplier_id</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.id</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.contract_id</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>proc.public.contract.id</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.po_order_id</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.id</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>proc.public.contract.supplier_id</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>proc.public.supplier.id</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>proc.public.goods_receipt.po_line_id</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>proc.public.po_line.id</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.po_order_id</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>proc.public.po_order.id</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>proc.public.payment.invoice_id</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>proc.public.invoice.id</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>REFERENCES</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
         <is>
           <t>active</t>
         </is>
